--- a/education_forms/042_student_loan_assistance_request_form--education_forms.xlsx
+++ b/education_forms/042_student_loan_assistance_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annual Income</t>
+          <t>Annual Income Hint</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>student_loan_assistance_request</t>
+          <t>student_loan_assistance_request_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Student Loan Assistance Request</t>
+          <t>Student Loan Assistance Request 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Student Loan Assistance Request</t>
+          <t>Student Loan Assistance Request Hint</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'federal_loans'}</t>
+          <t>federal_loans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Federal Loans'}</t>
+          <t>Federal Loans</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'private_loans'}</t>
+          <t>private_loans</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Private Loans'}</t>
+          <t>Private Loans</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'parent_loans'}</t>
+          <t>parent_loans</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Parent Loans'}</t>
+          <t>Parent Loans</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_6.9}</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 6.9}</t>
+          <t>6.9</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_7.0}</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 7.0}</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'making_payments'}</t>
+          <t>making_payments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Making Payments'}</t>
+          <t>Making Payments</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'behind_on_payments'}</t>
+          <t>behind_on_payments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Behind on Payments'}</t>
+          <t>Behind on Payments</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'in_default'}</t>
+          <t>in_default</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'In Default'}</t>
+          <t>In Default</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'incomplete'}</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Incomplete'}</t>
+          <t>Incomplete</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'standard_repayment'}</t>
+          <t>standard_repayment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Repayment'}</t>
+          <t>Standard Repayment</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'graduated_repayment'}</t>
+          <t>graduated_repayment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Graduated Repayment'}</t>
+          <t>Graduated Repayment</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'income-driven_repayment'}</t>
+          <t>income-driven_repayment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Income-Driven Repayment'}</t>
+          <t>Income-Driven Repayment</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'public_service_forgiveness'}</t>
+          <t>public_service_forgiveness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Public Service Forgiveness'}</t>
+          <t>Public Service Forgiveness</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'teacher_forgiveness'}</t>
+          <t>teacher_forgiveness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher Forgiveness'}</t>
+          <t>Teacher Forgiveness</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'perkins_loan_forgiveness'}</t>
+          <t>perkins_loan_forgiveness</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Perkins Loan Forgiveness'}</t>
+          <t>Perkins Loan Forgiveness</t>
         </is>
       </c>
     </row>
